--- a/unitydata/excel/reward_fixed.xlsx
+++ b/unitydata/excel/reward_fixed.xlsx
@@ -502,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B617"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.5" style="2" customWidth="1"/>
@@ -6040,6 +6040,26 @@
         <v>22</v>
       </c>
     </row>
+    <row r="618" spans="1:2">
+      <c r="A618" s="2">
+        <v>40004</v>
+      </c>
+      <c r="B618" s="4" t="inlineStr">
+        <is>
+          <t>[60002,57,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" s="2">
+        <v>40005</v>
+      </c>
+      <c r="B619" s="4" t="inlineStr">
+        <is>
+          <t>[60005,1001,1]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
